--- a/data/attendance/ECOLE_بن_يحي_BEM_فوج_1.xlsx
+++ b/data/attendance/ECOLE_بن_يحي_BEM_فوج_1.xlsx
@@ -3,9 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
-  <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
-  </bookViews>
   <sheets>
     <sheet sheetId="1" name="Présences" state="visible" r:id="rId4"/>
     <sheet sheetId="2" name="📖 Instructions" state="visible" r:id="rId5"/>
@@ -23,13 +20,6 @@
     <comment ref="B5" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c6a7343f-21aa-446a-8652-6b693011cecd</t>
         </r>
       </text>
@@ -37,13 +27,6 @@
     <comment ref="B6" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:14a64204-0302-447b-a108-ebaed0177b93</t>
         </r>
       </text>
@@ -51,13 +34,6 @@
     <comment ref="B7" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:27284445-6a3c-4e14-b620-a1c31ed242a7</t>
         </r>
       </text>
@@ -65,13 +41,6 @@
     <comment ref="B8" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4a536585-a7e2-488a-8cff-4fa3a082fdae</t>
         </r>
       </text>
@@ -79,13 +48,6 @@
     <comment ref="B9" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:98f5082f-9e1e-4761-8d05-62cd9f8ec3c3</t>
         </r>
       </text>
@@ -93,13 +55,6 @@
     <comment ref="B10" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d790c63f-42b2-4216-9b63-2ebb873b4696</t>
         </r>
       </text>
@@ -107,13 +62,6 @@
     <comment ref="B11" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a5e20413-5fca-43ee-9131-4e1744995ec2</t>
         </r>
       </text>
@@ -121,13 +69,6 @@
     <comment ref="B12" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:91dc8094-6cbd-459f-b2f4-cb8d7ffba0e0</t>
         </r>
       </text>
@@ -135,13 +76,6 @@
     <comment ref="B13" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:2932da96-6f3f-4b66-b48f-1336f520fbb3</t>
         </r>
       </text>
@@ -149,13 +83,6 @@
     <comment ref="B14" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:df961dd8-c013-4176-83ef-608177b3b522</t>
         </r>
       </text>
@@ -163,13 +90,6 @@
     <comment ref="B15" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:31db686a-e525-4eb9-8f8e-d4b7f06b670e</t>
         </r>
       </text>
@@ -177,13 +97,6 @@
     <comment ref="B16" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:aa17c078-c181-44c0-8f3d-12d550e077d2</t>
         </r>
       </text>
@@ -191,13 +104,6 @@
     <comment ref="B17" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:21370f93-156b-446b-8eea-d4f76eef008b</t>
         </r>
       </text>
@@ -205,13 +111,6 @@
     <comment ref="B18" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:80c8a090-8e2b-4fb6-8a86-03b1277f4e60</t>
         </r>
       </text>
@@ -219,13 +118,6 @@
     <comment ref="B19" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d02075ce-9b26-447f-8a2c-ea3c0532ea51</t>
         </r>
       </text>
@@ -233,13 +125,6 @@
     <comment ref="B20" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:fd525a30-7dea-4d43-acfb-b9989314d4fb</t>
         </r>
       </text>
@@ -247,13 +132,6 @@
     <comment ref="B21" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:96a226fa-95d1-4036-995a-5fbf604a2df4</t>
         </r>
       </text>
@@ -261,13 +139,6 @@
     <comment ref="B22" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d3e09d3a-c186-4c8b-990a-fa6d532348d3</t>
         </r>
       </text>
@@ -275,13 +146,6 @@
     <comment ref="B23" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d4e66531-c463-48c4-9ead-4a89d61e40c7</t>
         </r>
       </text>
@@ -289,13 +153,6 @@
     <comment ref="B24" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:a9d63b34-2821-4f99-8ce2-ee6c70bca5f3</t>
         </r>
       </text>
@@ -303,13 +160,6 @@
     <comment ref="B25" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:58db0313-7085-4ba0-90ab-eb9d7088058b</t>
         </r>
       </text>
@@ -317,13 +167,6 @@
     <comment ref="B26" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c4c52fac-d69f-4c85-b5c5-955cd97de81f</t>
         </r>
       </text>
@@ -331,13 +174,6 @@
     <comment ref="B27" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:c479ef3f-578c-4302-8e8e-4f9d1cc778dd</t>
         </r>
       </text>
@@ -345,13 +181,6 @@
     <comment ref="B28" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:afbcdd6f-57b6-4b1c-892c-2d75a817ea0e</t>
         </r>
       </text>
@@ -359,13 +188,6 @@
     <comment ref="B29" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:6cf59de9-8569-4977-a81f-2fddebc98c13</t>
         </r>
       </text>
@@ -373,13 +195,6 @@
     <comment ref="B30" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:d239f58c-6627-4490-9242-fd568893a027</t>
         </r>
       </text>
@@ -387,13 +202,6 @@
     <comment ref="B31" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:e635112e-1e1f-47d6-a697-fd6027e35651</t>
         </r>
       </text>
@@ -401,13 +209,6 @@
     <comment ref="B32" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:8bb714ba-590e-439f-a451-fe2d0e75a03f</t>
         </r>
       </text>
@@ -415,13 +216,6 @@
     <comment ref="B33" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:04054f56-9e4b-4a05-87a3-246add9eab27</t>
         </r>
       </text>
@@ -429,13 +223,6 @@
     <comment ref="B34" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:4d1d46f7-533a-4907-8559-6badbbbbfffb</t>
         </r>
       </text>
@@ -443,13 +230,6 @@
     <comment ref="B35" authorId="0">
       <text>
         <r>
-          <rPr>
-            <color theme="1"/>
-            <family val="2"/>
-            <scheme val="minor"/>
-            <sz val="11"/>
-            <rFont val="Calibri"/>
-          </rPr>
           <t>student_id:7f05d821-3ab1-4935-b66c-2727948128c8</t>
         </r>
       </text>
@@ -459,7 +239,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="54">
   <si>
     <t>بن يحي BEM فوج 1  |  ECOLE  |  4AM  |  بن يحيى عبد النور</t>
   </si>
@@ -473,6 +253,9 @@
     <t>has_books=false</t>
   </si>
   <si>
+    <t>is_formation=false</t>
+  </si>
+  <si>
     <t>حصة مجانية؟ (1 = نعم / 0 = عادية)</t>
   </si>
   <si>
@@ -485,6 +268,9 @@
     <t>25/09/2026</t>
   </si>
   <si>
+    <t>02/10/2026</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -578,7 +364,7 @@
     <t>لعرابة رسيم</t>
   </si>
   <si>
-    <t>حفناوي  دينا</t>
+    <t>حفناوي دينا</t>
   </si>
   <si>
     <t>تعليمات ملء الحضور والكتب / Instructions</t>
@@ -608,7 +394,10 @@
     <t>3. للأفواج التي لها كتب (ت1 / ت2 / ت3) :</t>
   </si>
   <si>
-    <t xml:space="preserve">   → اكتب 1 في خانة الفصل إذا استلم الطالب كتابه، أو 0 إذا لم يستلم</t>
+    <t xml:space="preserve">   → للأفواج التي لها كتابان في هذا الفصل (ت1): تم توفير عمودين (كتاب 1 ت 1 و كتاب 2 ت 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   → اكتب 1 (أو X) في خانة الكتاب إذا استلم الطالب نسخته، أو 0 إذا لم يستلم</t>
   </si>
   <si>
     <t>4. احفظ الملف (Ctrl+S) بعد الانتهاء ثم شغّل أمر الاستيراد.</t>
@@ -630,40 +419,33 @@
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="13"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFC00000"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <color rgb="FFFFFFFF"/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
-      <color rgb="FF666666"/>
+      <color rgb="666666"/>
       <sz val="9"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
-      <name val="Calibri"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="9">
@@ -750,7 +532,7 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1106,14 +888,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:N35"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
     <col min="3" max="14" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="27.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="28" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1131,7 +913,7 @@
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
     </row>
-    <row r="2" hidden="1" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" hidden="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -1141,10 +923,13 @@
       <c r="C2" t="s">
         <v>3</v>
       </c>
+      <c r="D2" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="3" ht="24" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="3">
@@ -1186,57 +971,57 @@
     </row>
     <row r="4" ht="42" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="I4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="M4" s="5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="5" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="6">
         <v>461</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C5" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D5" s="8">
         <v>0</v>
@@ -1272,15 +1057,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="6" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="6">
         <v>464</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C6" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D6" s="9">
         <v>0</v>
@@ -1316,15 +1101,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="6">
         <v>466</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="C7" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D7" s="8">
         <v>0</v>
@@ -1360,12 +1145,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="6">
         <v>473</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C8" s="9">
         <v>0</v>
@@ -1404,15 +1189,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="6">
         <v>477</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C9" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D9" s="8">
         <v>0</v>
@@ -1448,15 +1233,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="6">
         <v>478</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C10" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D10" s="9">
         <v>0</v>
@@ -1492,15 +1277,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="6">
         <v>481</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C11" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D11" s="8">
         <v>0</v>
@@ -1536,15 +1321,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="12" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" s="6">
         <v>486</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C12" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -1580,12 +1365,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="13" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="6">
         <v>754</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C13" s="8">
         <v>0</v>
@@ -1624,15 +1409,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="14" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" s="6">
         <v>755</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -1668,15 +1453,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="15" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="6">
         <v>756</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C15" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D15" s="8">
         <v>0</v>
@@ -1712,15 +1497,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="16" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="6">
         <v>757</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -1756,15 +1541,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="17" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="6">
         <v>758</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C17" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D17" s="8">
         <v>0</v>
@@ -1800,15 +1585,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="18" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="6">
         <v>759</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -1844,15 +1629,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="19" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="6">
         <v>760</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C19" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D19" s="8">
         <v>0</v>
@@ -1888,15 +1673,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="20" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>761</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C20" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -1932,15 +1717,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="21" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="6">
         <v>762</v>
       </c>
       <c r="B21" s="7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C21" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D21" s="8">
         <v>0</v>
@@ -1976,15 +1761,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="22" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="6">
         <v>763</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C22" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D22" s="9">
         <v>0</v>
@@ -2020,15 +1805,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="23" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="6">
         <v>764</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C23" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" s="8">
         <v>0</v>
@@ -2064,15 +1849,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="24" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="6">
         <v>765</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C24" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D24" s="9">
         <v>0</v>
@@ -2108,15 +1893,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="25" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="6">
         <v>766</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C25" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" s="8">
         <v>0</v>
@@ -2152,15 +1937,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="26" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="6">
         <v>767</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C26" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D26" s="9">
         <v>0</v>
@@ -2196,15 +1981,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="27" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="6">
         <v>768</v>
       </c>
       <c r="B27" s="7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="C27" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D27" s="8">
         <v>0</v>
@@ -2240,15 +2025,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="28" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="6">
         <v>769</v>
       </c>
       <c r="B28" s="7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C28" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D28" s="9">
         <v>0</v>
@@ -2284,15 +2069,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="29" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="6">
         <v>770</v>
       </c>
       <c r="B29" s="7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C29" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D29" s="8">
         <v>0</v>
@@ -2328,15 +2113,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="30" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="6">
         <v>771</v>
       </c>
       <c r="B30" s="7" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C30" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D30" s="9">
         <v>0</v>
@@ -2372,15 +2157,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="31" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="6">
         <v>772</v>
       </c>
       <c r="B31" s="7" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C31" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D31" s="8">
         <v>0</v>
@@ -2416,15 +2201,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="32" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="6">
         <v>773</v>
       </c>
       <c r="B32" s="7" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="C32" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D32" s="9">
         <v>0</v>
@@ -2460,15 +2245,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="33" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="6">
         <v>774</v>
       </c>
       <c r="B33" s="7" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C33" s="8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D33" s="8">
         <v>0</v>
@@ -2504,12 +2289,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="34" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="6">
         <v>775</v>
       </c>
       <c r="B34" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C34" s="9">
         <v>0</v>
@@ -2548,12 +2333,12 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" ht="18.95" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="35" ht="19" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="6">
         <v>824</v>
       </c>
       <c r="B35" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C35" s="8">
         <v>0</v>
@@ -2598,7 +2383,7 @@
     <mergeCell ref="A3:B3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -2608,89 +2393,94 @@
   <sheetPr>
     <tabColor rgb="FF70AD47"/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:A16"/>
+  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="17.25" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>8</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>50</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
 </file>